--- a/output_3b.xlsx
+++ b/output_3b.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>382768.4</v>
+        <v>382825</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>538710.4</v>
+        <v>538767</v>
       </c>
     </row>
     <row r="8">
@@ -582,10 +582,10 @@
         <v>35000</v>
       </c>
       <c r="D2" t="n">
-        <v>34869.33</v>
+        <v>34867</v>
       </c>
       <c r="E2" t="n">
-        <v>69869.33</v>
+        <v>69867</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -626,10 +626,10 @@
         <v>26000</v>
       </c>
       <c r="D4" t="n">
-        <v>46800</v>
+        <v>46814.4</v>
       </c>
       <c r="E4" t="n">
-        <v>72800</v>
+        <v>72814.39999999999</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -670,10 +670,10 @@
         <v>12500</v>
       </c>
       <c r="D6" t="n">
-        <v>87626.67</v>
+        <v>87643.2</v>
       </c>
       <c r="E6" t="n">
-        <v>100126.67</v>
+        <v>100143.2</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -714,10 +714,10 @@
         <v>27000</v>
       </c>
       <c r="D8" t="n">
-        <v>158936</v>
+        <v>158964</v>
       </c>
       <c r="E8" t="n">
-        <v>185936</v>
+        <v>185964</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -736,10 +736,10 @@
         <v>155500</v>
       </c>
       <c r="D9" t="n">
-        <v>382768.4</v>
+        <v>382825</v>
       </c>
       <c r="E9" t="n">
-        <v>538268.4</v>
+        <v>538325</v>
       </c>
       <c r="F9" t="n">
         <v>442</v>
@@ -802,19 +802,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -822,19 +822,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -842,19 +842,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -862,19 +862,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -882,19 +882,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -902,19 +902,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -922,19 +922,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -942,19 +942,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>133.33</v>
+        <v>132</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -965,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -982,19 +982,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>87.7</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>175.33</v>
+        <v>178</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1005,16 +1005,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -1045,16 +1045,16 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -1065,16 +1065,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -1085,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -1102,19 +1102,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>66.67</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1125,16 +1125,16 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -1145,16 +1145,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -1202,19 +1202,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -1222,19 +1222,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>66.67</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -1242,19 +1242,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -1262,19 +1262,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -1282,19 +1282,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -1302,19 +1302,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -1322,7 +1322,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1342,7 +1342,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2202.7</v>
+        <v>2214</v>
       </c>
       <c r="C2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="D2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1590,16 +1590,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3333.3</v>
+        <v>3329</v>
       </c>
       <c r="H2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="I2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="J2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1608,16 +1608,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3333.3</v>
+        <v>3329</v>
       </c>
       <c r="N2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="O2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="P2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2933.3</v>
+        <v>2934</v>
       </c>
       <c r="T2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="U2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="F3" t="n">
         <v>5000</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="L3" t="n">
         <v>5000</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="R3" t="n">
         <v>5000</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5326</v>
+        <v>5330</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5000</v>
+        <v>4998</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5000</v>
+        <v>4998</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15000</v>
+        <v>14986</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>18641</v>
+        <v>18669</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17500</v>
+        <v>17493</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>17500</v>
+        <v>17493</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2217.3</v>
+        <v>2220</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3333.3</v>
+        <v>3332</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3333.3</v>
+        <v>3332</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -2075,13 +2075,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2663</v>
+        <v>2667</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -2178,13 +2178,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>866.7</v>
+        <v>866</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>887.7</v>
+        <v>889</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>833.3</v>
+        <v>833</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>833.3</v>
+        <v>833</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2202.7</v>
+        <v>2214</v>
       </c>
       <c r="G2" t="n">
-        <v>5536</v>
+        <v>5547</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2549,13 +2549,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3333.3</v>
+        <v>3329</v>
       </c>
       <c r="L2" t="n">
-        <v>6666.7</v>
+        <v>6662</v>
       </c>
       <c r="M2" t="n">
-        <v>10000</v>
+        <v>9995</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -2567,13 +2567,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3333.3</v>
+        <v>3329</v>
       </c>
       <c r="R2" t="n">
-        <v>6666.7</v>
+        <v>6662</v>
       </c>
       <c r="S2" t="n">
-        <v>10000</v>
+        <v>9995</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -2585,10 +2585,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2933.3</v>
+        <v>2934</v>
       </c>
       <c r="X2" t="n">
-        <v>6266.7</v>
+        <v>6267</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>400</v>
       </c>
       <c r="G3" t="n">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -2731,10 +2731,10 @@
         <v>5200</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>4800</v>
       </c>
       <c r="I6" t="n">
-        <v>1333.3</v>
+        <v>1336</v>
       </c>
       <c r="J6" t="n">
-        <v>1333.3</v>
+        <v>1336</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -3128,46 +3128,46 @@
         <v>603</v>
       </c>
       <c r="J8" t="n">
-        <v>1359.7</v>
+        <v>1359</v>
       </c>
       <c r="K8" t="n">
-        <v>1073.7</v>
+        <v>1073</v>
       </c>
       <c r="L8" t="n">
-        <v>1720.3</v>
+        <v>1721</v>
       </c>
       <c r="M8" t="n">
-        <v>1508.3</v>
+        <v>1509</v>
       </c>
       <c r="N8" t="n">
-        <v>1309.3</v>
+        <v>1310</v>
       </c>
       <c r="O8" t="n">
-        <v>1073.3</v>
+        <v>1074</v>
       </c>
       <c r="P8" t="n">
-        <v>886.3</v>
+        <v>887</v>
       </c>
       <c r="Q8" t="n">
-        <v>700.3</v>
+        <v>701</v>
       </c>
       <c r="R8" t="n">
-        <v>1340.7</v>
+        <v>1341</v>
       </c>
       <c r="S8" t="n">
-        <v>1139.7</v>
+        <v>1140</v>
       </c>
       <c r="T8" t="n">
-        <v>911.7</v>
+        <v>912</v>
       </c>
       <c r="U8" t="n">
-        <v>674.7</v>
+        <v>675</v>
       </c>
       <c r="V8" t="n">
-        <v>421.7</v>
+        <v>422</v>
       </c>
       <c r="W8" t="n">
-        <v>212.7</v>
+        <v>213</v>
       </c>
       <c r="X8" t="n">
         <v>799</v>

--- a/output_3b.xlsx
+++ b/output_3b.xlsx
@@ -1002,7 +1002,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
@@ -1011,7 +1011,7 @@
         <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
@@ -1022,19 +1022,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1202,7 +1202,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>-0</v>
@@ -1211,7 +1211,7 @@
         <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>-0</v>

--- a/output_3b.xlsx
+++ b/output_3b.xlsx
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -971,7 +971,7 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F10" t="n">
         <v>-0</v>
@@ -1042,7 +1042,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
@@ -1051,7 +1051,7 @@
         <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
@@ -1062,7 +1062,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
@@ -1071,7 +1071,7 @@
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -1082,7 +1082,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
         <v>-0</v>
@@ -1091,7 +1091,7 @@
         <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F16" t="n">
         <v>-0</v>
@@ -1122,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C18" t="n">
         <v>-0</v>
@@ -1131,7 +1131,7 @@
         <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F18" t="n">
         <v>-0</v>
@@ -1142,7 +1142,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C19" t="n">
         <v>-0</v>
@@ -1151,7 +1151,7 @@
         <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F19" t="n">
         <v>-0</v>
@@ -1162,7 +1162,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
@@ -1171,7 +1171,7 @@
         <v>-0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F20" t="n">
         <v>-0</v>
@@ -1182,7 +1182,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
@@ -1191,7 +1191,7 @@
         <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F21" t="n">
         <v>-0</v>
@@ -1202,7 +1202,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
         <v>-0</v>
@@ -1211,7 +1211,7 @@
         <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F22" t="n">
         <v>-0</v>
